--- a/source_data/Figure7.xlsx
+++ b/source_data/Figure7.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Fig7A_ELISA" sheetId="2" r:id="rId2"/>
+    <sheet name="Fig7A_NS1" sheetId="2" r:id="rId2"/>
     <sheet name="Fig7B_IgM" sheetId="3" r:id="rId3"/>
     <sheet name="Fig7C_Hospitalization" sheetId="4" r:id="rId4"/>
     <sheet name="Fig7D_Serotype" sheetId="5" r:id="rId5"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="48">
   <si>
     <t>Sheet</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Rows</t>
   </si>
   <si>
-    <t>Figure 7 — Dengue clinical/laboratory profile (GraphPad source, through 2025)</t>
+    <t>Figure 7 — Dengue clinical/laboratory profile (clinical tables 2016-2026; 2026 = January-September)</t>
   </si>
   <si>
     <t>Generated by pipelines/build_source_data.R</t>
@@ -41,10 +41,10 @@
     <t>Incidence = cases per 100,000 inhabitants</t>
   </si>
   <si>
-    <t>Fig7A_ELISA</t>
+    <t>Fig7A_NS1</t>
   </si>
   <si>
-    <t>Dengue ELISA 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Dengue NS1 antigen 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>plot_proportion (graphpad_pipeline.R)</t>
@@ -53,19 +53,19 @@
     <t>Fig7B_IgM</t>
   </si>
   <si>
-    <t>Dengue IgM 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Dengue IgM 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig7C_Hospitalization</t>
   </si>
   <si>
-    <t>Dengue Hospitalization 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Dengue Hospitalization 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Fig7D_Serotype</t>
   </si>
   <si>
-    <t>Dengue Serotype 2016-2025: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
+    <t>Dengue Serotype 2016-2026: counts and plotted percentages. Percent = share of records with a known value; Excluded_missing rows (ignored/blank) are not plotted</t>
   </si>
   <si>
     <t>Virus</t>
@@ -92,7 +92,7 @@
     <t>Dengue</t>
   </si>
   <si>
-    <t>ELISA 2016-2025</t>
+    <t>NS1 antigen 2016-2026</t>
   </si>
   <si>
     <t>2016</t>
@@ -128,6 +128,9 @@
     <t>2025</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
     <t>Negative</t>
   </si>
   <si>
@@ -140,13 +143,13 @@
     <t>Not accomplished</t>
   </si>
   <si>
-    <t>IgM 2016-2025</t>
+    <t>IgM 2016-2026</t>
   </si>
   <si>
-    <t>Hospitalization 2016-2025</t>
+    <t>Hospitalization 2016-2026</t>
   </si>
   <si>
-    <t>Serotype 2016-2025</t>
+    <t>Serotype 2016-2026</t>
   </si>
   <si>
     <t>DENV 1</t>
@@ -544,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -558,7 +561,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -572,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -586,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -636,13 +639,13 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>97530</v>
+        <v>97528</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>12.88252636473149</v>
+        <v>12.91322026806769</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -659,13 +662,13 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>10098</v>
+        <v>10096</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>8.760909926949038</v>
+        <v>8.762747906088617</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -682,13 +685,13 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>11474</v>
+        <v>11389</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>8.155867049557875</v>
+        <v>8.127859095223481</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -705,13 +708,13 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>111741</v>
+        <v>111553</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>12.64181468491911</v>
+        <v>12.64353225062423</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -728,13 +731,13 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>98693</v>
+        <v>99013</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>18.42762210799315</v>
+        <v>18.40260353357941</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -751,13 +754,13 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>100571</v>
+        <v>101783</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>31.46560624737972</v>
+        <v>31.04683119965105</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -774,13 +777,13 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>338268</v>
+        <v>339998</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>37.42999883815499</v>
+        <v>37.1763723082508</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -797,13 +800,13 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>405299</v>
+        <v>405348</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>37.82326701257979</v>
+        <v>37.78841367120422</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -820,13 +823,13 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>1950923</v>
+        <v>1950869</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>45.62556142586559</v>
+        <v>45.62611251813415</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -843,13 +846,13 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>2.717407201567847</v>
+        <v>2.738109288327629</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -860,19 +863,19 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>11076</v>
+        <v>69380</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>1.463004839698206</v>
+        <v>24.38235810929538</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -883,19 +886,19 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>4801</v>
+        <v>11068</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4.165292984678385</v>
+        <v>1.465461425713366</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -906,19 +909,19 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
-        <v>5136</v>
+        <v>4798</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>3.650734980523727</v>
+        <v>4.164388317493382</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -929,19 +932,19 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>49599</v>
+        <v>5113</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>5.611381377983935</v>
+        <v>3.648937005345304</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -952,19 +955,19 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>42102</v>
+        <v>49509</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>7.861142593605703</v>
+        <v>5.611401201188268</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -975,19 +978,19 @@
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>19534</v>
+        <v>42257</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>6.111594320791435</v>
+        <v>7.853906229671511</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -998,19 +1001,19 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>47420</v>
+        <v>20083</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>5.247113368409988</v>
+        <v>6.125910132169341</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1021,19 +1024,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>97668</v>
+        <v>48034</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>9.114561947067825</v>
+        <v>5.252177564146021</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1044,19 +1047,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
-        <v>312112</v>
+        <v>97732</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>7.299255392319308</v>
+        <v>9.111028659112987</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1067,19 +1070,19 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>2952</v>
+        <v>312168</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>8.634861204551438</v>
+        <v>7.300855307332732</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1090,19 +1093,19 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
       </c>
       <c r="E22">
-        <v>361</v>
+        <v>2867</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.04768370775831097</v>
+        <v>8.459223415555293</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1113,19 +1116,19 @@
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
       </c>
       <c r="E23">
-        <v>146</v>
+        <v>49578</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.1266679391299821</v>
+        <v>17.42329994728519</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1136,19 +1139,19 @@
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24">
-        <v>132</v>
+        <v>360</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.09382730090131074</v>
+        <v>0.0476658938612949</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1159,19 +1162,19 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25">
-        <v>1142</v>
+        <v>146</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.129200135761964</v>
+        <v>0.1267196111617411</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1182,19 +1185,19 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26">
-        <v>1254</v>
+        <v>129</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.2341426253475263</v>
+        <v>0.09206197412273502</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1205,19 +1208,19 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>412</v>
+        <v>1144</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.128902265801478</v>
+        <v>0.1296621417148272</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1228,19 +1231,19 @@
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28">
-        <v>916</v>
+        <v>1257</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.1013571456234405</v>
+        <v>0.2336266211680216</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1251,19 +1254,19 @@
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29">
-        <v>3174</v>
+        <v>437</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.2962036656836762</v>
+        <v>0.1332979498958324</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1274,19 +1277,19 @@
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30">
-        <v>5288</v>
+        <v>936</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.123668627013971</v>
+        <v>0.1023449681484089</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1297,19 +1300,19 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>3178</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.06727703513031269</v>
+        <v>0.296267845523074</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1320,16 +1323,19 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
       </c>
       <c r="E32">
-        <v>761786</v>
+        <v>5288</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0.1236735439416452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1340,16 +1346,19 @@
         <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
       </c>
       <c r="E33">
-        <v>128074</v>
+        <v>23</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0.06786262244777529</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1360,16 +1369,19 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
       </c>
       <c r="E34">
-        <v>125702</v>
+        <v>392</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0.1377613776137762</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1380,13 +1392,13 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E35">
-        <v>672688</v>
+        <v>760276</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -1400,13 +1412,13 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E36">
-        <v>416938</v>
+        <v>128033</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -1420,13 +1432,13 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E37">
-        <v>212189</v>
+        <v>125337</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -1440,13 +1452,13 @@
         <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E38">
-        <v>490797</v>
+        <v>671833</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -1460,13 +1472,13 @@
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E39">
-        <v>573398</v>
+        <v>418425</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -1480,13 +1492,13 @@
         <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E40">
-        <v>2291199</v>
+        <v>212212</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -1500,13 +1512,13 @@
         <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E41">
-        <v>1607688</v>
+        <v>490541</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -1520,19 +1532,16 @@
         <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
         <v>39</v>
       </c>
       <c r="E42">
-        <v>648105</v>
+        <v>573278</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>85.60678508781199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1543,19 +1552,16 @@
         <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
       </c>
       <c r="E43">
-        <v>100217</v>
+        <v>2289151</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>86.9471291492426</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1566,19 +1572,16 @@
         <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
       </c>
       <c r="E44">
-        <v>123942</v>
+        <v>1609323</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>88.0995706690171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1589,19 +1592,16 @@
         <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
       </c>
       <c r="E45">
-        <v>721418</v>
+        <v>184000</v>
       </c>
       <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>81.61760380133499</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1612,19 +1612,19 @@
         <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E46">
-        <v>393522</v>
+        <v>646301</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>73.47709267305362</v>
+        <v>85.57365241235765</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1635,19 +1635,19 @@
         <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E47">
-        <v>199105</v>
+        <v>100175</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>62.29389716602737</v>
+        <v>86.94614416525626</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1658,19 +1658,19 @@
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E48">
-        <v>517131</v>
+        <v>123492</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>57.22153064781158</v>
+        <v>88.13114192530847</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1681,19 +1681,19 @@
         <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E49">
-        <v>565419</v>
+        <v>720087</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>52.76596737466871</v>
+        <v>81.61540440647268</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1704,19 +1704,19 @@
         <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E50">
-        <v>2007620</v>
+        <v>395511</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>46.95151455480113</v>
+        <v>73.50986361558105</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1727,19 +1727,134 @@
         <v>24</v>
       </c>
       <c r="C51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51">
+        <v>205534</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>62.69396071828378</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52">
+        <v>525586</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>57.46910515945477</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53">
+        <v>566420</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>52.80428982415972</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54">
+        <v>2007448</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>46.94935863059148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
         <v>35</v>
       </c>
-      <c r="D51" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51">
-        <v>30283</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>88.5804545587504</v>
+      <c r="D55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55">
+        <v>30074</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>88.7348046736693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56">
+        <v>165200</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>58.05658056580566</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -1780,7 +1895,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -1789,13 +1904,13 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>220155</v>
+        <v>219723</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>26.4095784879885</v>
+        <v>26.42562572386248</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1803,7 +1918,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -1812,13 +1927,13 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>30099</v>
+        <v>30086</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>24.06360678280474</v>
+        <v>24.06263996416917</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1826,7 +1941,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
@@ -1835,13 +1950,13 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>48797</v>
+        <v>48632</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>31.3647728806587</v>
+        <v>31.38095023004007</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1849,7 +1964,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -1858,13 +1973,13 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>297626</v>
+        <v>297097</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>30.85191957640366</v>
+        <v>30.85382140535331</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1872,7 +1987,7 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1881,13 +1996,13 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>235175</v>
+        <v>236027</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>39.2492777665588</v>
+        <v>39.21300526656809</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1895,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -1904,13 +2019,13 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>154051</v>
+        <v>155531</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>43.70377515326719</v>
+        <v>43.12519062803272</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1918,7 +2033,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
@@ -1927,13 +2042,13 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>271817</v>
+        <v>273930</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>30.60233747606175</v>
+        <v>30.47269216050976</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1941,7 +2056,7 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
@@ -1950,13 +2065,13 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>290650</v>
+        <v>290723</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>28.73790516342984</v>
+        <v>28.7125886889054</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1964,7 +2079,7 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
@@ -1973,13 +2088,13 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>723312</v>
+        <v>723225</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>20.32339883186649</v>
+        <v>20.32205065781654</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1987,7 +2102,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1996,13 +2111,13 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>1651</v>
+        <v>1633</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4.816359870474635</v>
+        <v>4.806899799835159</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2010,22 +2125,22 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>16311</v>
+        <v>55096</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>1.956651607810772</v>
+        <v>20.79965570484241</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2033,22 +2148,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>3902</v>
+        <v>16292</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>3.119578513123496</v>
+        <v>1.959404770065799</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2056,22 +2171,22 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
-        <v>4086</v>
+        <v>3901</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>2.626318462003227</v>
+        <v>3.120001279672404</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2079,22 +2194,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>19065</v>
+        <v>4072</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1.976278439128758</v>
+        <v>2.627554477231518</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2102,22 +2217,22 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>23512</v>
+        <v>19010</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>3.924009860092827</v>
+        <v>1.974207564922454</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2125,22 +2240,22 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>14133</v>
+        <v>23597</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>4.009486820865332</v>
+        <v>3.920353541227094</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2148,22 +2263,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>38938</v>
+        <v>14655</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>4.383809020932807</v>
+        <v>4.063496464716484</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2171,22 +2286,22 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>41645</v>
+        <v>39449</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>4.117633100055172</v>
+        <v>4.388410298397217</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2194,22 +2309,22 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
-        <v>201651</v>
+        <v>41801</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>5.665927978306333</v>
+        <v>4.128379659624228</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2217,22 +2332,22 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>1576</v>
+        <v>201643</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>4.59756702354211</v>
+        <v>5.666008864176571</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2240,22 +2355,22 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
       </c>
       <c r="E22">
-        <v>2775</v>
+        <v>1577</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.3328862860446871</v>
+        <v>4.642058165548098</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2263,22 +2378,22 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
       </c>
       <c r="E23">
-        <v>1099</v>
+        <v>15137</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.8786306473405234</v>
+        <v>5.714469079501225</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2286,22 +2401,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24">
-        <v>1087</v>
+        <v>2773</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.6986804131663014</v>
+        <v>0.3335029110847323</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2309,22 +2424,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25">
-        <v>5865</v>
+        <v>1099</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.6079660658531428</v>
+        <v>0.8789749824045046</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2332,22 +2447,22 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26">
-        <v>3473</v>
+        <v>1084</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.5796225860880566</v>
+        <v>0.6994766830351093</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2355,22 +2470,22 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>1771</v>
+        <v>5856</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.5024270260915943</v>
+        <v>0.6081514729187739</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2378,22 +2493,22 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28">
-        <v>2834</v>
+        <v>3487</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.3190640188331084</v>
+        <v>0.5793224900732667</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2401,22 +2516,22 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29">
-        <v>2978</v>
+        <v>1854</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.2944485861919631</v>
+        <v>0.5140718147788715</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2424,22 +2539,22 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30">
-        <v>8152</v>
+        <v>2884</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.2290523968596894</v>
+        <v>0.3208237293867416</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2447,22 +2562,22 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>334</v>
+        <v>2988</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.9743574783395081</v>
+        <v>0.2951029502394008</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2470,19 +2585,22 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
       </c>
       <c r="E32">
-        <v>685240</v>
+        <v>8147</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0.2289242583002957</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2490,19 +2608,22 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
       </c>
       <c r="E33">
-        <v>118255</v>
+        <v>330</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0.9713882020487461</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2510,19 +2631,22 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
       </c>
       <c r="E34">
-        <v>110807</v>
+        <v>1556</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0.5874158609832798</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2530,16 +2654,16 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E35">
-        <v>591896</v>
+        <v>684056</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -2550,16 +2674,16 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E36">
-        <v>353326</v>
+        <v>118216</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -2570,16 +2694,16 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E37">
-        <v>179322</v>
+        <v>110487</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -2590,16 +2714,16 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E38">
-        <v>506309</v>
+        <v>591208</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -2610,16 +2734,16 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E39">
-        <v>633576</v>
+        <v>354553</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -2630,16 +2754,16 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E40">
-        <v>3008131</v>
+        <v>179399</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -2650,16 +2774,16 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E41">
-        <v>1607596</v>
+        <v>506159</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -2670,22 +2794,19 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
         <v>39</v>
       </c>
       <c r="E42">
-        <v>594377</v>
+        <v>633428</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>71.30088361815604</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2693,22 +2814,19 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
       </c>
       <c r="E43">
-        <v>89981</v>
+        <v>3006105</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>71.93818405673123</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2716,22 +2834,19 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
       </c>
       <c r="E44">
-        <v>101609</v>
+        <v>1609243</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>65.31022824417178</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2739,22 +2854,19 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
       </c>
       <c r="E45">
-        <v>642136</v>
+        <v>203661</v>
       </c>
       <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>66.56383591861443</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2762,22 +2874,22 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" t="s">
         <v>40</v>
       </c>
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" t="s">
-        <v>39</v>
-      </c>
       <c r="E46">
-        <v>337023</v>
+        <v>592689</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>56.24708978726032</v>
+        <v>71.28146659498699</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2785,22 +2897,22 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
         <v>40</v>
       </c>
-      <c r="C47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" t="s">
-        <v>39</v>
-      </c>
       <c r="E47">
-        <v>182534</v>
+        <v>89946</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>51.78431099977588</v>
+        <v>71.93838377375393</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2808,22 +2920,22 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
         <v>40</v>
       </c>
-      <c r="C48" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" t="s">
-        <v>39</v>
-      </c>
       <c r="E48">
-        <v>574634</v>
+        <v>101185</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>64.69478948417233</v>
+        <v>65.2920186096933</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2831,22 +2943,22 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
         <v>40</v>
       </c>
-      <c r="C49" t="s">
-        <v>33</v>
-      </c>
-      <c r="D49" t="s">
-        <v>39</v>
-      </c>
       <c r="E49">
-        <v>676109</v>
+        <v>640955</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>66.85001315032302</v>
+        <v>66.56381955680546</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2854,22 +2966,22 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
         <v>40</v>
       </c>
-      <c r="C50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" t="s">
-        <v>39</v>
-      </c>
       <c r="E50">
-        <v>2625896</v>
+        <v>338799</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>73.78162079296749</v>
+        <v>56.28731870213155</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2877,22 +2989,137 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" t="s">
         <v>40</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51">
+        <v>188610</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>52.29724109247192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52">
+        <v>582673</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>64.81807381170628</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53">
+        <v>677016</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>66.86392870123098</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54">
+        <v>2625804</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>73.7830162197066</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s">
         <v>35</v>
       </c>
-      <c r="D51" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51">
-        <v>30718</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>89.61171562764375</v>
+      <c r="D55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55">
+        <v>30432</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>89.579653832568</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56">
+        <v>193100</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>72.89845935467308</v>
       </c>
     </row>
   </sheetData>
@@ -2902,7 +3129,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -2933,7 +3160,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -2942,13 +3169,13 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>32265</v>
+        <v>32221</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>4.715933174503413</v>
+        <v>4.717334715402162</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2956,7 +3183,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -2965,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>11599</v>
+        <v>11597</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>8.714042086441735</v>
+        <v>8.715158529162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2979,7 +3206,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
@@ -2988,13 +3215,13 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>15100</v>
+        <v>15044</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>9.097481624292083</v>
+        <v>9.097341065629781</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3002,7 +3229,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -3011,13 +3238,13 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>56196</v>
+        <v>56057</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5.465043115646404</v>
+        <v>5.462500548130753</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3025,7 +3252,7 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3034,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>31872</v>
+        <v>32092</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>4.793351390616329</v>
+        <v>4.804565624869002</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3048,7 +3275,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -3057,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>16923</v>
+        <v>17079</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>4.581894976241725</v>
+        <v>4.523447556188851</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3071,7 +3298,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
@@ -3080,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>49798</v>
+        <v>50111</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>4.879559215045324</v>
+        <v>4.858876265478814</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3094,7 +3321,7 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
@@ -3103,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>53134</v>
+        <v>53178</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>4.360031214587157</v>
+        <v>4.359670790664805</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3117,7 +3344,7 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
@@ -3126,13 +3353,13 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>190330</v>
+        <v>190252</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>4.102590410892763</v>
+        <v>4.102500849602283</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3140,7 +3367,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -3149,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>71986</v>
+        <v>72313</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>5.769315537945035</v>
+        <v>5.775535778323191</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3163,22 +3390,22 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>651905</v>
+        <v>29595</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>95.28406682549658</v>
+        <v>8.564111468009376</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3186,22 +3413,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>121508</v>
+        <v>650813</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>91.28595791355826</v>
+        <v>95.28266528459784</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3209,22 +3436,22 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
-        <v>150880</v>
+        <v>121470</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>90.90251837570791</v>
+        <v>91.28484147083799</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3232,22 +3459,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>972085</v>
+        <v>150323</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>94.53495688435359</v>
+        <v>90.90265893437022</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3255,22 +3482,22 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>633049</v>
+        <v>970158</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>95.20664860938368</v>
+        <v>94.53749945186925</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3278,22 +3505,22 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>352422</v>
+        <v>635856</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>95.41810502375827</v>
+        <v>95.195434375131</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3301,22 +3528,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>970745</v>
+        <v>360487</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>95.12044078495467</v>
+        <v>95.47655244381114</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3324,22 +3551,22 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>1165527</v>
+        <v>981218</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>95.63996878541285</v>
+        <v>95.14112373452119</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3347,22 +3574,22 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
-        <v>4448934</v>
+        <v>1166593</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>95.89740958910724</v>
+        <v>95.64032920933519</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3370,22 +3597,22 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>1175753</v>
+        <v>4447212</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>94.23068446205497</v>
+        <v>95.89749915039772</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3393,19 +3620,22 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22">
-        <v>834688</v>
+        <v>1179744</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>94.22446422167681</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3413,19 +3643,22 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23">
-        <v>110229</v>
+        <v>315975</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>91.43588853199063</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3433,16 +3666,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E24">
-        <v>100406</v>
+        <v>832499</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -3453,16 +3686,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25">
-        <v>528307</v>
+        <v>110181</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -3473,16 +3706,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E26">
-        <v>287588</v>
+        <v>100093</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -3493,16 +3726,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E27">
-        <v>162466</v>
+        <v>527911</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -3513,16 +3746,16 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28">
-        <v>373989</v>
+        <v>288515</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -3533,16 +3766,16 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29">
-        <v>426297</v>
+        <v>162483</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -3553,16 +3786,16 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30">
-        <v>1927878</v>
+        <v>373766</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -3573,18 +3806,78 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31">
+        <v>426185</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32">
+        <v>1927460</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
         <v>35</v>
       </c>
-      <c r="D31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31">
-        <v>394136</v>
-      </c>
-      <c r="F31" t="b">
+      <c r="D33" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33">
+        <v>391158</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34">
+        <v>122980</v>
+      </c>
+      <c r="F34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3595,7 +3888,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -3626,22 +3919,22 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>93.08484551250613</v>
+        <v>93.10429447852761</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3649,13 +3942,13 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>283</v>
@@ -3672,13 +3965,13 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>456</v>
@@ -3687,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>39.04109589041096</v>
+        <v>39.37823834196891</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3695,22 +3988,22 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>4213</v>
+        <v>4198</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>33.36501148332937</v>
+        <v>33.34922148077534</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3718,22 +4011,22 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>2070</v>
+        <v>2085</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>28.74201610663705</v>
+        <v>28.75068946497518</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3741,22 +4034,22 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>2739</v>
+        <v>2755</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>63.52040816326531</v>
+        <v>63.66997920036977</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3764,22 +4057,22 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>18188</v>
+        <v>18256</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>87.93270160510539</v>
+        <v>87.95529003661592</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3787,22 +4080,22 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>40852</v>
+        <v>40854</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>86.9246973211056</v>
+        <v>86.92525372880274</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3810,22 +4103,22 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>129955</v>
+        <v>129949</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>68.53516016411943</v>
+        <v>68.54464799058987</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3833,22 +4126,22 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>5900</v>
+        <v>5921</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>12.11747792154446</v>
+        <v>12.08910122912328</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3856,22 +4149,22 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>44</v>
       </c>
       <c r="E12">
-        <v>134</v>
+        <v>1876</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>3.285924472780775</v>
+        <v>5.611390284757118</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3879,22 +4172,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>37.29433272394881</v>
+        <v>3.263803680981595</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3902,22 +4195,22 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14">
-        <v>697</v>
+        <v>204</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>59.67465753424658</v>
+        <v>37.29433272394881</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3925,22 +4218,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
-        <v>8006</v>
+        <v>687</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>63.40381721707452</v>
+        <v>59.32642487046632</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3948,22 +4241,22 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16">
-        <v>5091</v>
+        <v>7982</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>70.68869758400444</v>
+        <v>63.40959644105497</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3971,22 +4264,22 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17">
-        <v>1560</v>
+        <v>5126</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>36.17810760667903</v>
+        <v>70.68394925537783</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3994,22 +4287,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18">
-        <v>2473</v>
+        <v>1559</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>11.95610133436473</v>
+        <v>36.02958169632539</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4017,22 +4310,22 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19">
-        <v>6022</v>
+        <v>2474</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>12.81358384577739</v>
+        <v>11.91944497976489</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4040,22 +4333,22 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E20">
-        <v>57814</v>
+        <v>6021</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>30.48972143994769</v>
+        <v>12.81091087044405</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4063,22 +4356,22 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21">
-        <v>35957</v>
+        <v>57790</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>73.84883959745328</v>
+        <v>30.48269095857751</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4086,22 +4379,22 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
         <v>45</v>
       </c>
       <c r="E22">
-        <v>42</v>
+        <v>36162</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1.029916625796959</v>
+        <v>73.83314957736127</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4109,22 +4402,22 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>21465</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1.645338208409506</v>
+        <v>64.20495333811917</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4132,22 +4425,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24">
         <v>42</v>
       </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.2568493150684931</v>
+        <v>1.030674846625767</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4155,22 +4448,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.07919537499010057</v>
+        <v>1.645338208409506</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4178,13 +4471,13 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -4193,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.04165509580672035</v>
+        <v>0.2590673575129534</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4201,22 +4494,22 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.06957328385899814</v>
+        <v>0.07944073721004132</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4224,22 +4517,22 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.01933861922258751</v>
+        <v>0.04136789851075565</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -4247,22 +4540,22 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.2255463114666894</v>
+        <v>0.06933210076265311</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4270,22 +4563,22 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30">
-        <v>1794</v>
+        <v>6</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.9461127108185932</v>
+        <v>0.0289073039121218</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4293,22 +4586,22 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31">
-        <v>6792</v>
+        <v>106</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>13.94947627849661</v>
+        <v>0.2255367135470968</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4316,22 +4609,22 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
         <v>46</v>
       </c>
       <c r="E32">
-        <v>106</v>
+        <v>1789</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>2.599313388916135</v>
+        <v>0.9436500108132058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4339,22 +4632,22 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>46</v>
       </c>
       <c r="E33">
-        <v>51</v>
+        <v>6857</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>9.323583180987203</v>
+        <v>14.00016333864184</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4362,22 +4655,22 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>9977</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>1.027397260273972</v>
+        <v>29.84266570949988</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4385,22 +4678,22 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35">
-        <v>398</v>
+        <v>106</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>3.151975924606003</v>
+        <v>2.601226993865031</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4408,22 +4701,22 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E36">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.5276312135517912</v>
+        <v>9.323583180987203</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4431,22 +4724,22 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.2319109461966605</v>
+        <v>1.036269430051814</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4454,22 +4747,22 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E38">
-        <v>19</v>
+        <v>398</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.09185844130729065</v>
+        <v>3.161741340959644</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4477,22 +4770,22 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.0361725216503181</v>
+        <v>0.5239933811362383</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4500,22 +4793,22 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0.0290056851142824</v>
+        <v>0.231107002542177</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4523,22 +4816,22 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E41">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.08420620250564798</v>
+        <v>0.09635767970707265</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4546,19 +4839,22 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E42">
-        <v>1514780</v>
+        <v>18</v>
       </c>
       <c r="F42" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0.03829868720611077</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4566,19 +4862,22 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E43">
-        <v>242789</v>
+        <v>55</v>
       </c>
       <c r="F43" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0.02901104001941102</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4586,19 +4885,22 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44">
         <v>38</v>
       </c>
-      <c r="E44">
-        <v>265218</v>
-      </c>
       <c r="F44" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0.07758585487361672</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4606,19 +4908,22 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E45">
-        <v>1543961</v>
+        <v>114</v>
       </c>
       <c r="F45" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0.3409906676238335</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4626,16 +4931,16 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E46">
-        <v>945307</v>
+        <v>1511458</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -4646,16 +4951,16 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E47">
-        <v>527499</v>
+        <v>242701</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -4666,16 +4971,16 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E48">
-        <v>1373848</v>
+        <v>264302</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -4686,16 +4991,16 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E49">
-        <v>1597961</v>
+        <v>1541538</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -4706,16 +5011,16 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E50">
-        <v>6377524</v>
+        <v>949211</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -4726,18 +5031,118 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51">
+        <v>535722</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52">
+        <v>1384339</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53">
+        <v>1598957</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54">
+        <v>6375341</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
         <v>35</v>
       </c>
-      <c r="D51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51">
-        <v>1593185</v>
-      </c>
-      <c r="F51" t="b">
+      <c r="D55" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55">
+        <v>1594237</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56">
+        <v>435118</v>
+      </c>
+      <c r="F56" t="b">
         <v>1</v>
       </c>
     </row>
